--- a/AAII_Financials/Yearly/UTGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UTGN_YR_FIN.xlsx
@@ -2267,10 +2267,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>5300</v>
+        <v>800</v>
       </c>
       <c r="F43" s="3">
         <v>2100</v>
@@ -2369,10 +2369,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>24300</v>
+        <v>28400</v>
       </c>
       <c r="E45" s="3">
-        <v>24800</v>
+        <v>29300</v>
       </c>
       <c r="F45" s="3">
         <v>30600</v>
